--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF630EEC-3D47-452F-B05F-365604768B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3CEE03B-6FDE-4932-899B-E3ED28823C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3CEE03B-6FDE-4932-899B-E3ED28823C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84F18C63-1317-46A3-878A-AE300FDF4FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84F18C63-1317-46A3-878A-AE300FDF4FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79416FB4-48DA-475A-8840-19E14DBCCD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79416FB4-48DA-475A-8840-19E14DBCCD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{719036A4-AB16-4471-9F70-6296A4DB5B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{719036A4-AB16-4471-9F70-6296A4DB5B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9E31A18-E5FA-4AFB-8E15-3853723E26AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9E31A18-E5FA-4AFB-8E15-3853723E26AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7273AFC3-16FA-489B-B9F7-A280F8A478BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7273AFC3-16FA-489B-B9F7-A280F8A478BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{458A77C3-B9F6-44F6-B3D6-89E8476C1287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,6 +40,32 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{2FF9EF2B-EBD7-4C7E-9F26-8FF1228838F5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Amit Kanudia:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+11-09-2025
+AFS will be sufficient
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D8" authorId="0" shapeId="0" xr:uid="{79577DE7-359E-49C1-A1D9-EC64BAD436CB}">
       <text>
         <r>
@@ -97,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="93">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -358,6 +384,9 @@
   </si>
   <si>
     <t>base-year nuclear capacity</t>
+  </si>
+  <si>
+    <t>\I: hydro</t>
   </si>
   <si>
     <t>geothermal</t>
@@ -968,15 +997,12 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="4">
-        <f>IFERROR(VLOOKUP(B5,$F$3:$J$11,5,FALSE),"")</f>
-        <v>0.31127604163438005</v>
-      </c>
+      <c r="D5" s="4"/>
       <c r="F5" t="s">
         <v>8</v>
       </c>
@@ -1004,7 +1030,7 @@
         <v/>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -1253,7 +1279,7 @@
     </row>
     <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G11" s="3">
         <v>0.15298675050527735</v>
@@ -1603,12 +1629,12 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
         <v>69</v>
@@ -1637,7 +1663,7 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -1958,7 +1984,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B10">
         <v>2000</v>
@@ -2084,7 +2110,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B19">
         <v>2001</v>
@@ -2210,7 +2236,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B28">
         <v>2002</v>
@@ -2336,7 +2362,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B37">
         <v>2003</v>
@@ -2462,7 +2488,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B46">
         <v>2004</v>
@@ -2588,7 +2614,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B55">
         <v>2005</v>
@@ -2714,7 +2740,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B64">
         <v>2006</v>
@@ -2840,7 +2866,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B73">
         <v>2007</v>
@@ -2966,7 +2992,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B82">
         <v>2008</v>
@@ -3092,7 +3118,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B91">
         <v>2009</v>
@@ -3218,7 +3244,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B100">
         <v>2010</v>
@@ -3344,7 +3370,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B109">
         <v>2011</v>
@@ -3470,7 +3496,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B118">
         <v>2012</v>
@@ -3596,7 +3622,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B127">
         <v>2013</v>
@@ -3722,7 +3748,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B136">
         <v>2014</v>
@@ -3848,7 +3874,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B145">
         <v>2015</v>
@@ -3974,7 +4000,7 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B154">
         <v>2016</v>
@@ -4100,7 +4126,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B163">
         <v>2017</v>
@@ -4226,7 +4252,7 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B172">
         <v>2018</v>
@@ -4352,7 +4378,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B181">
         <v>2019</v>
@@ -4478,7 +4504,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B190">
         <v>2020</v>
@@ -4604,7 +4630,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B199">
         <v>2021</v>
@@ -4730,7 +4756,7 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B208">
         <v>2022</v>
@@ -4856,7 +4882,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B217">
         <v>2023</v>
@@ -4979,7 +5005,7 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B226">
         <v>2000</v>
@@ -5102,7 +5128,7 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B235">
         <v>2001</v>
@@ -5225,7 +5251,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B244">
         <v>2002</v>
@@ -5348,7 +5374,7 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B253">
         <v>2003</v>
@@ -5471,7 +5497,7 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B262">
         <v>2004</v>
@@ -5594,7 +5620,7 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B271">
         <v>2005</v>
@@ -5717,7 +5743,7 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B280">
         <v>2006</v>
@@ -5840,7 +5866,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B289">
         <v>2007</v>
@@ -5963,7 +5989,7 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B298">
         <v>2008</v>
@@ -6086,7 +6112,7 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B307">
         <v>2009</v>
@@ -6209,7 +6235,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B316">
         <v>2010</v>
@@ -6332,7 +6358,7 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B325">
         <v>2011</v>
@@ -6455,7 +6481,7 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B334">
         <v>2012</v>
@@ -6578,7 +6604,7 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B343">
         <v>2013</v>
@@ -6701,7 +6727,7 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B352">
         <v>2014</v>
@@ -6824,7 +6850,7 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B361">
         <v>2015</v>
@@ -6947,7 +6973,7 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B370">
         <v>2016</v>
@@ -7070,7 +7096,7 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B379">
         <v>2017</v>
@@ -7193,7 +7219,7 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B388">
         <v>2018</v>
@@ -7316,7 +7342,7 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B397">
         <v>2019</v>
@@ -7439,7 +7465,7 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B406">
         <v>2020</v>
@@ -7562,7 +7588,7 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B415">
         <v>2021</v>
@@ -7685,7 +7711,7 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B424">
         <v>2022</v>
@@ -7808,7 +7834,7 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B433">
         <v>2023</v>
@@ -7934,7 +7960,7 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B442">
         <v>2000</v>
@@ -8060,7 +8086,7 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B451">
         <v>2001</v>
@@ -8186,7 +8212,7 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B460">
         <v>2002</v>
@@ -8312,7 +8338,7 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B469">
         <v>2003</v>
@@ -8438,7 +8464,7 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B478">
         <v>2004</v>
@@ -8564,7 +8590,7 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B487">
         <v>2005</v>
@@ -8690,7 +8716,7 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B496">
         <v>2006</v>
@@ -8816,7 +8842,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B505">
         <v>2007</v>
@@ -8942,7 +8968,7 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B514">
         <v>2008</v>
@@ -9068,7 +9094,7 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B523">
         <v>2009</v>
@@ -9194,7 +9220,7 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B532">
         <v>2010</v>
@@ -9320,7 +9346,7 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B541">
         <v>2011</v>
@@ -9446,7 +9472,7 @@
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B550">
         <v>2012</v>
@@ -9572,7 +9598,7 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B559">
         <v>2013</v>
@@ -9698,7 +9724,7 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B568">
         <v>2014</v>
@@ -9824,7 +9850,7 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B577">
         <v>2015</v>
@@ -9950,7 +9976,7 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B586">
         <v>2016</v>
@@ -10076,7 +10102,7 @@
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A595" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B595">
         <v>2017</v>
@@ -10202,7 +10228,7 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A604" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B604">
         <v>2018</v>
@@ -10328,7 +10354,7 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A613" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B613">
         <v>2019</v>
@@ -10454,7 +10480,7 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A622" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B622">
         <v>2020</v>
@@ -10580,7 +10606,7 @@
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A631" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B631">
         <v>2021</v>
@@ -10706,7 +10732,7 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A640" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B640">
         <v>2022</v>
@@ -10832,7 +10858,7 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A649" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B649">
         <v>2023</v>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{458A77C3-B9F6-44F6-B3D6-89E8476C1287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BA15D3B-4453-40FD-B31D-8DA4A4669F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BA15D3B-4453-40FD-B31D-8DA4A4669F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0C29720-9F68-4751-9CCB-F4569E9219E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0C29720-9F68-4751-9CCB-F4569E9219E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{807E377E-D6E0-4B2A-A842-84349EEDFB22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{807E377E-D6E0-4B2A-A842-84349EEDFB22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17D61407-C4D8-4FFB-BFF9-EA8BD8052D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17D61407-C4D8-4FFB-BFF9-EA8BD8052D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BBE5EC0B-42E0-4BFB-B785-B1AAEAE965DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BBE5EC0B-42E0-4BFB-B785-B1AAEAE965DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{92EEC90A-2348-41EA-A887-73343061A85A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92EEC90A-2348-41EA-A887-73343061A85A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD741509-4329-444D-A475-02827A5E3DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD741509-4329-444D-A475-02827A5E3DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DA2FD54-4769-4674-BED9-A4FD2190A191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DA2FD54-4769-4674-BED9-A4FD2190A191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCB37170-B9BD-43E0-B02D-4C3462E214AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1496E4E7-3290-4047-BC5A-75A5FCF8715D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{71A658C6-2D93-4E4F-8879-105932CD2519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71A658C6-2D93-4E4F-8879-105932CD2519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E556AFE0-FE89-42C7-8AEB-D9B6E889AFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E556AFE0-FE89-42C7-8AEB-D9B6E889AFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37F4C4CC-1DFB-4A75-8E7A-4629B3C9E47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37F4C4CC-1DFB-4A75-8E7A-4629B3C9E47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8342A97-0658-4299-A721-77E2C5939BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12682" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8342A97-0658-4299-A721-77E2C5939BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CEA0B58-705A-41B4-A511-FF73830327C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12682" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CEA0B58-705A-41B4-A511-FF73830327C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6D928EB-EA2C-4B2E-98D3-CE06AC8DF433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6D928EB-EA2C-4B2E-98D3-CE06AC8DF433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA0B1D1A-A32C-48EC-9836-676270485E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA0B1D1A-A32C-48EC-9836-676270485E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7CE2106-2FD3-49EB-91EC-11C49FB3CF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Base_VS.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FBD1DF8-4728-484A-BFEB-B6A0DC195D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{845B2AF4-050A-43FC-944A-300B3ECF9E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Veda" sheetId="1" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="5" r:id="rId2"/>
+    <sheet name="re_targets" sheetId="5" r:id="rId1"/>
+    <sheet name="Veda" sheetId="1" r:id="rId2"/>
     <sheet name="buildrates" sheetId="4" r:id="rId3"/>
     <sheet name="historical_data_long" sheetId="3" r:id="rId4"/>
   </sheets>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2127" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2129" uniqueCount="133">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -390,6 +390,9 @@
     <t>\I: hydro</t>
   </si>
   <si>
+    <t>UCE_min oil fleet utilization</t>
+  </si>
+  <si>
     <t>geothermal</t>
   </si>
   <si>
@@ -527,8 +530,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -656,7 +660,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -669,6 +673,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1010,6 +1015,1208 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB07601F-D0C0-4121-8DC9-4B812BA026DC}">
+  <dimension ref="B9:L43"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I10" t="s">
+        <v>100</v>
+      </c>
+      <c r="J10" t="s">
+        <v>101</v>
+      </c>
+      <c r="K10" t="s">
+        <v>102</v>
+      </c>
+      <c r="L10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B11">
+        <v>2030</v>
+      </c>
+      <c r="C11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G11" t="s">
+        <v>107</v>
+      </c>
+      <c r="H11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I11" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J11" t="s">
+        <v>109</v>
+      </c>
+      <c r="K11" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B12">
+        <v>2030</v>
+      </c>
+      <c r="C12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12">
+        <v>3.24</v>
+      </c>
+      <c r="F12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I12" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K12" t="s">
+        <v>110</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B13">
+        <v>2030</v>
+      </c>
+      <c r="C13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E13">
+        <v>19.41</v>
+      </c>
+      <c r="F13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H13" t="s">
+        <v>108</v>
+      </c>
+      <c r="I13" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J13" t="s">
+        <v>109</v>
+      </c>
+      <c r="K13" t="s">
+        <v>110</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B14">
+        <v>2030</v>
+      </c>
+      <c r="C14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" t="s">
+        <v>105</v>
+      </c>
+      <c r="E14">
+        <v>2.1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" t="s">
+        <v>107</v>
+      </c>
+      <c r="H14" t="s">
+        <v>108</v>
+      </c>
+      <c r="I14" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J14" t="s">
+        <v>109</v>
+      </c>
+      <c r="K14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B15">
+        <v>2030</v>
+      </c>
+      <c r="C15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15">
+        <v>26.04</v>
+      </c>
+      <c r="F15" t="s">
+        <v>106</v>
+      </c>
+      <c r="G15" t="s">
+        <v>107</v>
+      </c>
+      <c r="H15" t="s">
+        <v>108</v>
+      </c>
+      <c r="I15" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J15" t="s">
+        <v>109</v>
+      </c>
+      <c r="K15" t="s">
+        <v>110</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B16">
+        <v>2030</v>
+      </c>
+      <c r="C16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" t="s">
+        <v>107</v>
+      </c>
+      <c r="H16" t="s">
+        <v>108</v>
+      </c>
+      <c r="I16" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J16" t="s">
+        <v>109</v>
+      </c>
+      <c r="K16" t="s">
+        <v>110</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B17">
+        <v>2030</v>
+      </c>
+      <c r="C17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17">
+        <v>7.5</v>
+      </c>
+      <c r="F17" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" t="s">
+        <v>107</v>
+      </c>
+      <c r="H17" t="s">
+        <v>108</v>
+      </c>
+      <c r="I17" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J17" t="s">
+        <v>109</v>
+      </c>
+      <c r="K17" t="s">
+        <v>110</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B18">
+        <v>2030</v>
+      </c>
+      <c r="C18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D18" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18">
+        <v>79.17</v>
+      </c>
+      <c r="F18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18" t="s">
+        <v>107</v>
+      </c>
+      <c r="H18" t="s">
+        <v>108</v>
+      </c>
+      <c r="I18" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J18" t="s">
+        <v>109</v>
+      </c>
+      <c r="K18" t="s">
+        <v>110</v>
+      </c>
+      <c r="L18" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B19">
+        <v>2030</v>
+      </c>
+      <c r="C19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19">
+        <v>10.9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>106</v>
+      </c>
+      <c r="G19" t="s">
+        <v>107</v>
+      </c>
+      <c r="H19" t="s">
+        <v>108</v>
+      </c>
+      <c r="I19" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J19" t="s">
+        <v>109</v>
+      </c>
+      <c r="K19" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B20">
+        <v>2030</v>
+      </c>
+      <c r="C20" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20">
+        <v>104</v>
+      </c>
+      <c r="F20" t="s">
+        <v>106</v>
+      </c>
+      <c r="G20" t="s">
+        <v>107</v>
+      </c>
+      <c r="H20" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J20" t="s">
+        <v>109</v>
+      </c>
+      <c r="K20" t="s">
+        <v>110</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B21">
+        <v>2030</v>
+      </c>
+      <c r="C21" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21">
+        <v>46.9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21" t="s">
+        <v>107</v>
+      </c>
+      <c r="H21" t="s">
+        <v>108</v>
+      </c>
+      <c r="I21" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J21" t="s">
+        <v>109</v>
+      </c>
+      <c r="K21" t="s">
+        <v>110</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B22">
+        <v>2030</v>
+      </c>
+      <c r="C22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" t="s">
+        <v>119</v>
+      </c>
+      <c r="E22">
+        <v>7.5</v>
+      </c>
+      <c r="F22" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" t="s">
+        <v>107</v>
+      </c>
+      <c r="H22" t="s">
+        <v>108</v>
+      </c>
+      <c r="I22" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K22" t="s">
+        <v>110</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B23">
+        <v>2030</v>
+      </c>
+      <c r="C23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" t="s">
+        <v>119</v>
+      </c>
+      <c r="E23">
+        <v>97.6</v>
+      </c>
+      <c r="F23" t="s">
+        <v>106</v>
+      </c>
+      <c r="G23" t="s">
+        <v>107</v>
+      </c>
+      <c r="H23" t="s">
+        <v>108</v>
+      </c>
+      <c r="I23" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J23" t="s">
+        <v>109</v>
+      </c>
+      <c r="K23" t="s">
+        <v>110</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B24">
+        <v>2030</v>
+      </c>
+      <c r="C24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24" t="s">
+        <v>119</v>
+      </c>
+      <c r="E24">
+        <v>64.8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" t="s">
+        <v>107</v>
+      </c>
+      <c r="H24" t="s">
+        <v>108</v>
+      </c>
+      <c r="I24" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J24" t="s">
+        <v>109</v>
+      </c>
+      <c r="K24" t="s">
+        <v>110</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B25">
+        <v>2030</v>
+      </c>
+      <c r="C25" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25">
+        <v>3.29</v>
+      </c>
+      <c r="F25" t="s">
+        <v>106</v>
+      </c>
+      <c r="G25" t="s">
+        <v>107</v>
+      </c>
+      <c r="H25" t="s">
+        <v>108</v>
+      </c>
+      <c r="I25" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J25" t="s">
+        <v>109</v>
+      </c>
+      <c r="K25" t="s">
+        <v>110</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B26">
+        <v>2030</v>
+      </c>
+      <c r="C26" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" t="s">
+        <v>122</v>
+      </c>
+      <c r="E26">
+        <v>31.35</v>
+      </c>
+      <c r="F26" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" t="s">
+        <v>107</v>
+      </c>
+      <c r="H26" t="s">
+        <v>108</v>
+      </c>
+      <c r="I26" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J26" t="s">
+        <v>109</v>
+      </c>
+      <c r="K26" t="s">
+        <v>110</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B27">
+        <v>2030</v>
+      </c>
+      <c r="C27" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27">
+        <v>14.14</v>
+      </c>
+      <c r="F27" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" t="s">
+        <v>107</v>
+      </c>
+      <c r="H27" t="s">
+        <v>108</v>
+      </c>
+      <c r="I27" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J27" t="s">
+        <v>109</v>
+      </c>
+      <c r="K27" t="s">
+        <v>110</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B28">
+        <v>2030</v>
+      </c>
+      <c r="C28" t="s">
+        <v>116</v>
+      </c>
+      <c r="D28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E28">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="F28" t="s">
+        <v>106</v>
+      </c>
+      <c r="G28" t="s">
+        <v>107</v>
+      </c>
+      <c r="H28" t="s">
+        <v>108</v>
+      </c>
+      <c r="I28" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J28" t="s">
+        <v>109</v>
+      </c>
+      <c r="K28" t="s">
+        <v>110</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B29">
+        <v>2030</v>
+      </c>
+      <c r="C29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" t="s">
+        <v>122</v>
+      </c>
+      <c r="F29" t="s">
+        <v>106</v>
+      </c>
+      <c r="G29" t="s">
+        <v>107</v>
+      </c>
+      <c r="H29" t="s">
+        <v>108</v>
+      </c>
+      <c r="I29" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J29" t="s">
+        <v>109</v>
+      </c>
+      <c r="K29" t="s">
+        <v>110</v>
+      </c>
+      <c r="L29" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B30">
+        <v>2030</v>
+      </c>
+      <c r="C30" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" t="s">
+        <v>122</v>
+      </c>
+      <c r="E30">
+        <v>29.42</v>
+      </c>
+      <c r="F30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G30" t="s">
+        <v>107</v>
+      </c>
+      <c r="H30" t="s">
+        <v>108</v>
+      </c>
+      <c r="I30" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J30" t="s">
+        <v>109</v>
+      </c>
+      <c r="K30" t="s">
+        <v>110</v>
+      </c>
+      <c r="L30" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="B31">
+        <v>2030</v>
+      </c>
+      <c r="C31" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31">
+        <v>19.54</v>
+      </c>
+      <c r="F31" t="s">
+        <v>106</v>
+      </c>
+      <c r="G31" t="s">
+        <v>107</v>
+      </c>
+      <c r="H31" t="s">
+        <v>108</v>
+      </c>
+      <c r="I31" s="13">
+        <v>45474</v>
+      </c>
+      <c r="J31" t="s">
+        <v>109</v>
+      </c>
+      <c r="K31" t="s">
+        <v>110</v>
+      </c>
+      <c r="L31" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B32">
+        <v>2030</v>
+      </c>
+      <c r="C32" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" t="s">
+        <v>105</v>
+      </c>
+      <c r="E32">
+        <v>3.05</v>
+      </c>
+      <c r="F32" t="s">
+        <v>124</v>
+      </c>
+      <c r="G32" t="s">
+        <v>125</v>
+      </c>
+      <c r="H32" t="s">
+        <v>126</v>
+      </c>
+      <c r="I32" s="13">
+        <v>45108</v>
+      </c>
+      <c r="J32" t="s">
+        <v>127</v>
+      </c>
+      <c r="K32" t="s">
+        <v>128</v>
+      </c>
+      <c r="L32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B33">
+        <v>2030</v>
+      </c>
+      <c r="C33" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" t="s">
+        <v>105</v>
+      </c>
+      <c r="E33">
+        <v>19.170000000000002</v>
+      </c>
+      <c r="F33" t="s">
+        <v>124</v>
+      </c>
+      <c r="G33" t="s">
+        <v>125</v>
+      </c>
+      <c r="H33" t="s">
+        <v>126</v>
+      </c>
+      <c r="I33" s="13">
+        <v>45108</v>
+      </c>
+      <c r="J33" t="s">
+        <v>127</v>
+      </c>
+      <c r="K33" t="s">
+        <v>128</v>
+      </c>
+      <c r="L33" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B34">
+        <v>2030</v>
+      </c>
+      <c r="C34" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" t="s">
+        <v>105</v>
+      </c>
+      <c r="E34">
+        <v>2.1</v>
+      </c>
+      <c r="F34" t="s">
+        <v>124</v>
+      </c>
+      <c r="G34" t="s">
+        <v>125</v>
+      </c>
+      <c r="H34" t="s">
+        <v>126</v>
+      </c>
+      <c r="I34" s="13">
+        <v>45108</v>
+      </c>
+      <c r="J34" t="s">
+        <v>127</v>
+      </c>
+      <c r="K34" t="s">
+        <v>128</v>
+      </c>
+      <c r="L34" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B35">
+        <v>2030</v>
+      </c>
+      <c r="C35" t="s">
+        <v>115</v>
+      </c>
+      <c r="D35" t="s">
+        <v>105</v>
+      </c>
+      <c r="E35">
+        <v>26.04</v>
+      </c>
+      <c r="F35" t="s">
+        <v>124</v>
+      </c>
+      <c r="G35" t="s">
+        <v>125</v>
+      </c>
+      <c r="H35" t="s">
+        <v>126</v>
+      </c>
+      <c r="I35" s="13">
+        <v>45108</v>
+      </c>
+      <c r="J35" t="s">
+        <v>127</v>
+      </c>
+      <c r="K35" t="s">
+        <v>128</v>
+      </c>
+      <c r="L35" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B36">
+        <v>2030</v>
+      </c>
+      <c r="C36" t="s">
+        <v>116</v>
+      </c>
+      <c r="D36" t="s">
+        <v>105</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>124</v>
+      </c>
+      <c r="G36" t="s">
+        <v>125</v>
+      </c>
+      <c r="H36" t="s">
+        <v>126</v>
+      </c>
+      <c r="I36" s="13">
+        <v>45108</v>
+      </c>
+      <c r="J36" t="s">
+        <v>127</v>
+      </c>
+      <c r="K36" t="s">
+        <v>128</v>
+      </c>
+      <c r="L36" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B37">
+        <v>2030</v>
+      </c>
+      <c r="C37" t="s">
+        <v>118</v>
+      </c>
+      <c r="D37" t="s">
+        <v>105</v>
+      </c>
+      <c r="E37">
+        <v>79.92</v>
+      </c>
+      <c r="F37" t="s">
+        <v>124</v>
+      </c>
+      <c r="G37" t="s">
+        <v>125</v>
+      </c>
+      <c r="H37" t="s">
+        <v>126</v>
+      </c>
+      <c r="I37" s="13">
+        <v>45108</v>
+      </c>
+      <c r="J37" t="s">
+        <v>127</v>
+      </c>
+      <c r="K37" t="s">
+        <v>128</v>
+      </c>
+      <c r="L37" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B38">
+        <v>2030</v>
+      </c>
+      <c r="C38" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" t="s">
+        <v>119</v>
+      </c>
+      <c r="E38">
+        <v>9.6</v>
+      </c>
+      <c r="F38" t="s">
+        <v>124</v>
+      </c>
+      <c r="G38" t="s">
+        <v>125</v>
+      </c>
+      <c r="H38" t="s">
+        <v>126</v>
+      </c>
+      <c r="I38" s="13">
+        <v>45108</v>
+      </c>
+      <c r="J38" t="s">
+        <v>127</v>
+      </c>
+      <c r="K38" t="s">
+        <v>128</v>
+      </c>
+      <c r="L38" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B39">
+        <v>2030</v>
+      </c>
+      <c r="C39" t="s">
+        <v>113</v>
+      </c>
+      <c r="D39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E39">
+        <v>46.9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>124</v>
+      </c>
+      <c r="G39" t="s">
+        <v>125</v>
+      </c>
+      <c r="H39" t="s">
+        <v>126</v>
+      </c>
+      <c r="I39" s="13">
+        <v>45108</v>
+      </c>
+      <c r="J39" t="s">
+        <v>127</v>
+      </c>
+      <c r="K39" t="s">
+        <v>128</v>
+      </c>
+      <c r="L39" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B40">
+        <v>2030</v>
+      </c>
+      <c r="C40" t="s">
+        <v>116</v>
+      </c>
+      <c r="D40" t="s">
+        <v>119</v>
+      </c>
+      <c r="E40">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>124</v>
+      </c>
+      <c r="G40" t="s">
+        <v>125</v>
+      </c>
+      <c r="H40" t="s">
+        <v>126</v>
+      </c>
+      <c r="I40" s="13">
+        <v>45108</v>
+      </c>
+      <c r="J40" t="s">
+        <v>127</v>
+      </c>
+      <c r="K40" t="s">
+        <v>128</v>
+      </c>
+      <c r="L40" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B41">
+        <v>2030</v>
+      </c>
+      <c r="C41" t="s">
+        <v>118</v>
+      </c>
+      <c r="D41" t="s">
+        <v>119</v>
+      </c>
+      <c r="E41">
+        <v>99.1</v>
+      </c>
+      <c r="F41" t="s">
+        <v>124</v>
+      </c>
+      <c r="G41" t="s">
+        <v>125</v>
+      </c>
+      <c r="H41" t="s">
+        <v>126</v>
+      </c>
+      <c r="I41" s="13">
+        <v>45108</v>
+      </c>
+      <c r="J41" t="s">
+        <v>127</v>
+      </c>
+      <c r="K41" t="s">
+        <v>128</v>
+      </c>
+      <c r="L41" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B42">
+        <v>2030</v>
+      </c>
+      <c r="C42" t="s">
+        <v>121</v>
+      </c>
+      <c r="D42" t="s">
+        <v>119</v>
+      </c>
+      <c r="E42">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="F42" t="s">
+        <v>124</v>
+      </c>
+      <c r="G42" t="s">
+        <v>125</v>
+      </c>
+      <c r="H42" t="s">
+        <v>126</v>
+      </c>
+      <c r="I42" s="13">
+        <v>45108</v>
+      </c>
+      <c r="J42" t="s">
+        <v>127</v>
+      </c>
+      <c r="K42" t="s">
+        <v>128</v>
+      </c>
+      <c r="L42" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B43">
+        <v>2030</v>
+      </c>
+      <c r="C43" t="s">
+        <v>123</v>
+      </c>
+      <c r="D43" t="s">
+        <v>122</v>
+      </c>
+      <c r="E43">
+        <v>72</v>
+      </c>
+      <c r="F43" t="s">
+        <v>124</v>
+      </c>
+      <c r="G43" t="s">
+        <v>125</v>
+      </c>
+      <c r="H43" t="s">
+        <v>126</v>
+      </c>
+      <c r="I43" s="13">
+        <v>45108</v>
+      </c>
+      <c r="J43" t="s">
+        <v>127</v>
+      </c>
+      <c r="K43" t="s">
+        <v>128</v>
+      </c>
+      <c r="L43" t="s">
+        <v>129</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AL40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1040,7 +2247,7 @@
     <col min="33" max="33" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="7" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="7.86328125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="5.265625" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.19921875" bestFit="1" customWidth="1"/>
   </cols>
@@ -1153,7 +2360,7 @@
         <v/>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -1399,10 +2606,34 @@
       <c r="J10" s="3">
         <v>0.14275360852558924</v>
       </c>
+      <c r="AF10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH10">
+        <f>-1/8.76</f>
+        <v>-0.11415525114155252</v>
+      </c>
+      <c r="AI10" s="2">
+        <f>VLOOKUP(AG10,$F$3:$J$11,2,FALSE)</f>
+        <v>0.88232496194824972</v>
+      </c>
+      <c r="AJ10" s="12">
+        <f>AI10*$AD$1</f>
+        <v>0.17646499238964997</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G11" s="3">
         <v>0.15298675050527735</v>
@@ -1730,1208 +2961,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93AFF057-AE73-4AC3-9994-630DD90707C1}">
-  <dimension ref="B9:L43"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F10" t="s">
-        <v>96</v>
-      </c>
-      <c r="G10" t="s">
-        <v>97</v>
-      </c>
-      <c r="H10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I10" t="s">
-        <v>99</v>
-      </c>
-      <c r="J10" t="s">
-        <v>100</v>
-      </c>
-      <c r="K10" t="s">
-        <v>101</v>
-      </c>
-      <c r="L10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B11">
-        <v>2030</v>
-      </c>
-      <c r="C11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D11" t="s">
-        <v>104</v>
-      </c>
-      <c r="E11">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>105</v>
-      </c>
-      <c r="G11" t="s">
-        <v>106</v>
-      </c>
-      <c r="H11" t="s">
-        <v>107</v>
-      </c>
-      <c r="I11" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J11" t="s">
-        <v>108</v>
-      </c>
-      <c r="K11" t="s">
-        <v>109</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B12">
-        <v>2030</v>
-      </c>
-      <c r="C12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12">
-        <v>3.24</v>
-      </c>
-      <c r="F12" t="s">
-        <v>105</v>
-      </c>
-      <c r="G12" t="s">
-        <v>106</v>
-      </c>
-      <c r="H12" t="s">
-        <v>107</v>
-      </c>
-      <c r="I12" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J12" t="s">
-        <v>108</v>
-      </c>
-      <c r="K12" t="s">
-        <v>109</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B13">
-        <v>2030</v>
-      </c>
-      <c r="C13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D13" t="s">
-        <v>104</v>
-      </c>
-      <c r="E13">
-        <v>19.41</v>
-      </c>
-      <c r="F13" t="s">
-        <v>105</v>
-      </c>
-      <c r="G13" t="s">
-        <v>106</v>
-      </c>
-      <c r="H13" t="s">
-        <v>107</v>
-      </c>
-      <c r="I13" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J13" t="s">
-        <v>108</v>
-      </c>
-      <c r="K13" t="s">
-        <v>109</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B14">
-        <v>2030</v>
-      </c>
-      <c r="C14" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14">
-        <v>2.1</v>
-      </c>
-      <c r="F14" t="s">
-        <v>105</v>
-      </c>
-      <c r="G14" t="s">
-        <v>106</v>
-      </c>
-      <c r="H14" t="s">
-        <v>107</v>
-      </c>
-      <c r="I14" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J14" t="s">
-        <v>108</v>
-      </c>
-      <c r="K14" t="s">
-        <v>109</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B15">
-        <v>2030</v>
-      </c>
-      <c r="C15" t="s">
-        <v>114</v>
-      </c>
-      <c r="D15" t="s">
-        <v>104</v>
-      </c>
-      <c r="E15">
-        <v>26.04</v>
-      </c>
-      <c r="F15" t="s">
-        <v>105</v>
-      </c>
-      <c r="G15" t="s">
-        <v>106</v>
-      </c>
-      <c r="H15" t="s">
-        <v>107</v>
-      </c>
-      <c r="I15" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J15" t="s">
-        <v>108</v>
-      </c>
-      <c r="K15" t="s">
-        <v>109</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B16">
-        <v>2030</v>
-      </c>
-      <c r="C16" t="s">
-        <v>115</v>
-      </c>
-      <c r="D16" t="s">
-        <v>104</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s">
-        <v>105</v>
-      </c>
-      <c r="G16" t="s">
-        <v>106</v>
-      </c>
-      <c r="H16" t="s">
-        <v>107</v>
-      </c>
-      <c r="I16" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J16" t="s">
-        <v>108</v>
-      </c>
-      <c r="K16" t="s">
-        <v>109</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B17">
-        <v>2030</v>
-      </c>
-      <c r="C17" t="s">
-        <v>116</v>
-      </c>
-      <c r="D17" t="s">
-        <v>104</v>
-      </c>
-      <c r="E17">
-        <v>7.5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>105</v>
-      </c>
-      <c r="G17" t="s">
-        <v>106</v>
-      </c>
-      <c r="H17" t="s">
-        <v>107</v>
-      </c>
-      <c r="I17" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J17" t="s">
-        <v>108</v>
-      </c>
-      <c r="K17" t="s">
-        <v>109</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B18">
-        <v>2030</v>
-      </c>
-      <c r="C18" t="s">
-        <v>117</v>
-      </c>
-      <c r="D18" t="s">
-        <v>104</v>
-      </c>
-      <c r="E18">
-        <v>79.17</v>
-      </c>
-      <c r="F18" t="s">
-        <v>105</v>
-      </c>
-      <c r="G18" t="s">
-        <v>106</v>
-      </c>
-      <c r="H18" t="s">
-        <v>107</v>
-      </c>
-      <c r="I18" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J18" t="s">
-        <v>108</v>
-      </c>
-      <c r="K18" t="s">
-        <v>109</v>
-      </c>
-      <c r="L18" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B19">
-        <v>2030</v>
-      </c>
-      <c r="C19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19">
-        <v>10.9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>105</v>
-      </c>
-      <c r="G19" t="s">
-        <v>106</v>
-      </c>
-      <c r="H19" t="s">
-        <v>107</v>
-      </c>
-      <c r="I19" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J19" t="s">
-        <v>108</v>
-      </c>
-      <c r="K19" t="s">
-        <v>109</v>
-      </c>
-      <c r="L19" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B20">
-        <v>2030</v>
-      </c>
-      <c r="C20" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" t="s">
-        <v>118</v>
-      </c>
-      <c r="E20">
-        <v>104</v>
-      </c>
-      <c r="F20" t="s">
-        <v>105</v>
-      </c>
-      <c r="G20" t="s">
-        <v>106</v>
-      </c>
-      <c r="H20" t="s">
-        <v>107</v>
-      </c>
-      <c r="I20" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J20" t="s">
-        <v>108</v>
-      </c>
-      <c r="K20" t="s">
-        <v>109</v>
-      </c>
-      <c r="L20" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B21">
-        <v>2030</v>
-      </c>
-      <c r="C21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D21" t="s">
-        <v>118</v>
-      </c>
-      <c r="E21">
-        <v>46.9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>105</v>
-      </c>
-      <c r="G21" t="s">
-        <v>106</v>
-      </c>
-      <c r="H21" t="s">
-        <v>107</v>
-      </c>
-      <c r="I21" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J21" t="s">
-        <v>108</v>
-      </c>
-      <c r="K21" t="s">
-        <v>109</v>
-      </c>
-      <c r="L21" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B22">
-        <v>2030</v>
-      </c>
-      <c r="C22" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22">
-        <v>7.5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>105</v>
-      </c>
-      <c r="G22" t="s">
-        <v>106</v>
-      </c>
-      <c r="H22" t="s">
-        <v>107</v>
-      </c>
-      <c r="I22" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J22" t="s">
-        <v>108</v>
-      </c>
-      <c r="K22" t="s">
-        <v>109</v>
-      </c>
-      <c r="L22" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B23">
-        <v>2030</v>
-      </c>
-      <c r="C23" t="s">
-        <v>117</v>
-      </c>
-      <c r="D23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E23">
-        <v>97.6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>105</v>
-      </c>
-      <c r="G23" t="s">
-        <v>106</v>
-      </c>
-      <c r="H23" t="s">
-        <v>107</v>
-      </c>
-      <c r="I23" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J23" t="s">
-        <v>108</v>
-      </c>
-      <c r="K23" t="s">
-        <v>109</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B24">
-        <v>2030</v>
-      </c>
-      <c r="C24" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" t="s">
-        <v>118</v>
-      </c>
-      <c r="E24">
-        <v>64.8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>105</v>
-      </c>
-      <c r="G24" t="s">
-        <v>106</v>
-      </c>
-      <c r="H24" t="s">
-        <v>107</v>
-      </c>
-      <c r="I24" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J24" t="s">
-        <v>108</v>
-      </c>
-      <c r="K24" t="s">
-        <v>109</v>
-      </c>
-      <c r="L24" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B25">
-        <v>2030</v>
-      </c>
-      <c r="C25" t="s">
-        <v>111</v>
-      </c>
-      <c r="D25" t="s">
-        <v>121</v>
-      </c>
-      <c r="E25">
-        <v>3.29</v>
-      </c>
-      <c r="F25" t="s">
-        <v>105</v>
-      </c>
-      <c r="G25" t="s">
-        <v>106</v>
-      </c>
-      <c r="H25" t="s">
-        <v>107</v>
-      </c>
-      <c r="I25" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J25" t="s">
-        <v>108</v>
-      </c>
-      <c r="K25" t="s">
-        <v>109</v>
-      </c>
-      <c r="L25" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B26">
-        <v>2030</v>
-      </c>
-      <c r="C26" t="s">
-        <v>119</v>
-      </c>
-      <c r="D26" t="s">
-        <v>121</v>
-      </c>
-      <c r="E26">
-        <v>31.35</v>
-      </c>
-      <c r="F26" t="s">
-        <v>105</v>
-      </c>
-      <c r="G26" t="s">
-        <v>106</v>
-      </c>
-      <c r="H26" t="s">
-        <v>107</v>
-      </c>
-      <c r="I26" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J26" t="s">
-        <v>108</v>
-      </c>
-      <c r="K26" t="s">
-        <v>109</v>
-      </c>
-      <c r="L26" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B27">
-        <v>2030</v>
-      </c>
-      <c r="C27" t="s">
-        <v>112</v>
-      </c>
-      <c r="D27" t="s">
-        <v>121</v>
-      </c>
-      <c r="E27">
-        <v>14.14</v>
-      </c>
-      <c r="F27" t="s">
-        <v>105</v>
-      </c>
-      <c r="G27" t="s">
-        <v>106</v>
-      </c>
-      <c r="H27" t="s">
-        <v>107</v>
-      </c>
-      <c r="I27" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J27" t="s">
-        <v>108</v>
-      </c>
-      <c r="K27" t="s">
-        <v>109</v>
-      </c>
-      <c r="L27" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B28">
-        <v>2030</v>
-      </c>
-      <c r="C28" t="s">
-        <v>115</v>
-      </c>
-      <c r="D28" t="s">
-        <v>121</v>
-      </c>
-      <c r="E28">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="F28" t="s">
-        <v>105</v>
-      </c>
-      <c r="G28" t="s">
-        <v>106</v>
-      </c>
-      <c r="H28" t="s">
-        <v>107</v>
-      </c>
-      <c r="I28" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J28" t="s">
-        <v>108</v>
-      </c>
-      <c r="K28" t="s">
-        <v>109</v>
-      </c>
-      <c r="L28" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B29">
-        <v>2030</v>
-      </c>
-      <c r="C29" t="s">
-        <v>122</v>
-      </c>
-      <c r="D29" t="s">
-        <v>121</v>
-      </c>
-      <c r="F29" t="s">
-        <v>105</v>
-      </c>
-      <c r="G29" t="s">
-        <v>106</v>
-      </c>
-      <c r="H29" t="s">
-        <v>107</v>
-      </c>
-      <c r="I29" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J29" t="s">
-        <v>108</v>
-      </c>
-      <c r="K29" t="s">
-        <v>109</v>
-      </c>
-      <c r="L29" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B30">
-        <v>2030</v>
-      </c>
-      <c r="C30" t="s">
-        <v>117</v>
-      </c>
-      <c r="D30" t="s">
-        <v>121</v>
-      </c>
-      <c r="E30">
-        <v>29.42</v>
-      </c>
-      <c r="F30" t="s">
-        <v>105</v>
-      </c>
-      <c r="G30" t="s">
-        <v>106</v>
-      </c>
-      <c r="H30" t="s">
-        <v>107</v>
-      </c>
-      <c r="I30" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J30" t="s">
-        <v>108</v>
-      </c>
-      <c r="K30" t="s">
-        <v>109</v>
-      </c>
-      <c r="L30" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B31">
-        <v>2030</v>
-      </c>
-      <c r="C31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D31" t="s">
-        <v>121</v>
-      </c>
-      <c r="E31">
-        <v>19.54</v>
-      </c>
-      <c r="F31" t="s">
-        <v>105</v>
-      </c>
-      <c r="G31" t="s">
-        <v>106</v>
-      </c>
-      <c r="H31" t="s">
-        <v>107</v>
-      </c>
-      <c r="I31" s="12">
-        <v>45474</v>
-      </c>
-      <c r="J31" t="s">
-        <v>108</v>
-      </c>
-      <c r="K31" t="s">
-        <v>109</v>
-      </c>
-      <c r="L31" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B32">
-        <v>2030</v>
-      </c>
-      <c r="C32" t="s">
-        <v>111</v>
-      </c>
-      <c r="D32" t="s">
-        <v>104</v>
-      </c>
-      <c r="E32">
-        <v>3.05</v>
-      </c>
-      <c r="F32" t="s">
-        <v>123</v>
-      </c>
-      <c r="G32" t="s">
-        <v>124</v>
-      </c>
-      <c r="H32" t="s">
-        <v>125</v>
-      </c>
-      <c r="I32" s="12">
-        <v>45108</v>
-      </c>
-      <c r="J32" t="s">
-        <v>126</v>
-      </c>
-      <c r="K32" t="s">
-        <v>127</v>
-      </c>
-      <c r="L32" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B33">
-        <v>2030</v>
-      </c>
-      <c r="C33" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" t="s">
-        <v>104</v>
-      </c>
-      <c r="E33">
-        <v>19.170000000000002</v>
-      </c>
-      <c r="F33" t="s">
-        <v>123</v>
-      </c>
-      <c r="G33" t="s">
-        <v>124</v>
-      </c>
-      <c r="H33" t="s">
-        <v>125</v>
-      </c>
-      <c r="I33" s="12">
-        <v>45108</v>
-      </c>
-      <c r="J33" t="s">
-        <v>126</v>
-      </c>
-      <c r="K33" t="s">
-        <v>127</v>
-      </c>
-      <c r="L33" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B34">
-        <v>2030</v>
-      </c>
-      <c r="C34" t="s">
-        <v>113</v>
-      </c>
-      <c r="D34" t="s">
-        <v>104</v>
-      </c>
-      <c r="E34">
-        <v>2.1</v>
-      </c>
-      <c r="F34" t="s">
-        <v>123</v>
-      </c>
-      <c r="G34" t="s">
-        <v>124</v>
-      </c>
-      <c r="H34" t="s">
-        <v>125</v>
-      </c>
-      <c r="I34" s="12">
-        <v>45108</v>
-      </c>
-      <c r="J34" t="s">
-        <v>126</v>
-      </c>
-      <c r="K34" t="s">
-        <v>127</v>
-      </c>
-      <c r="L34" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B35">
-        <v>2030</v>
-      </c>
-      <c r="C35" t="s">
-        <v>114</v>
-      </c>
-      <c r="D35" t="s">
-        <v>104</v>
-      </c>
-      <c r="E35">
-        <v>26.04</v>
-      </c>
-      <c r="F35" t="s">
-        <v>123</v>
-      </c>
-      <c r="G35" t="s">
-        <v>124</v>
-      </c>
-      <c r="H35" t="s">
-        <v>125</v>
-      </c>
-      <c r="I35" s="12">
-        <v>45108</v>
-      </c>
-      <c r="J35" t="s">
-        <v>126</v>
-      </c>
-      <c r="K35" t="s">
-        <v>127</v>
-      </c>
-      <c r="L35" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B36">
-        <v>2030</v>
-      </c>
-      <c r="C36" t="s">
-        <v>115</v>
-      </c>
-      <c r="D36" t="s">
-        <v>104</v>
-      </c>
-      <c r="E36">
-        <v>1</v>
-      </c>
-      <c r="F36" t="s">
-        <v>123</v>
-      </c>
-      <c r="G36" t="s">
-        <v>124</v>
-      </c>
-      <c r="H36" t="s">
-        <v>125</v>
-      </c>
-      <c r="I36" s="12">
-        <v>45108</v>
-      </c>
-      <c r="J36" t="s">
-        <v>126</v>
-      </c>
-      <c r="K36" t="s">
-        <v>127</v>
-      </c>
-      <c r="L36" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B37">
-        <v>2030</v>
-      </c>
-      <c r="C37" t="s">
-        <v>117</v>
-      </c>
-      <c r="D37" t="s">
-        <v>104</v>
-      </c>
-      <c r="E37">
-        <v>79.92</v>
-      </c>
-      <c r="F37" t="s">
-        <v>123</v>
-      </c>
-      <c r="G37" t="s">
-        <v>124</v>
-      </c>
-      <c r="H37" t="s">
-        <v>125</v>
-      </c>
-      <c r="I37" s="12">
-        <v>45108</v>
-      </c>
-      <c r="J37" t="s">
-        <v>126</v>
-      </c>
-      <c r="K37" t="s">
-        <v>127</v>
-      </c>
-      <c r="L37" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B38">
-        <v>2030</v>
-      </c>
-      <c r="C38" t="s">
-        <v>111</v>
-      </c>
-      <c r="D38" t="s">
-        <v>118</v>
-      </c>
-      <c r="E38">
-        <v>9.6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G38" t="s">
-        <v>124</v>
-      </c>
-      <c r="H38" t="s">
-        <v>125</v>
-      </c>
-      <c r="I38" s="12">
-        <v>45108</v>
-      </c>
-      <c r="J38" t="s">
-        <v>126</v>
-      </c>
-      <c r="K38" t="s">
-        <v>127</v>
-      </c>
-      <c r="L38" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B39">
-        <v>2030</v>
-      </c>
-      <c r="C39" t="s">
-        <v>112</v>
-      </c>
-      <c r="D39" t="s">
-        <v>118</v>
-      </c>
-      <c r="E39">
-        <v>46.9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>123</v>
-      </c>
-      <c r="G39" t="s">
-        <v>124</v>
-      </c>
-      <c r="H39" t="s">
-        <v>125</v>
-      </c>
-      <c r="I39" s="12">
-        <v>45108</v>
-      </c>
-      <c r="J39" t="s">
-        <v>126</v>
-      </c>
-      <c r="K39" t="s">
-        <v>127</v>
-      </c>
-      <c r="L39" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B40">
-        <v>2030</v>
-      </c>
-      <c r="C40" t="s">
-        <v>115</v>
-      </c>
-      <c r="D40" t="s">
-        <v>118</v>
-      </c>
-      <c r="E40">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>123</v>
-      </c>
-      <c r="G40" t="s">
-        <v>124</v>
-      </c>
-      <c r="H40" t="s">
-        <v>125</v>
-      </c>
-      <c r="I40" s="12">
-        <v>45108</v>
-      </c>
-      <c r="J40" t="s">
-        <v>126</v>
-      </c>
-      <c r="K40" t="s">
-        <v>127</v>
-      </c>
-      <c r="L40" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B41">
-        <v>2030</v>
-      </c>
-      <c r="C41" t="s">
-        <v>117</v>
-      </c>
-      <c r="D41" t="s">
-        <v>118</v>
-      </c>
-      <c r="E41">
-        <v>99.1</v>
-      </c>
-      <c r="F41" t="s">
-        <v>123</v>
-      </c>
-      <c r="G41" t="s">
-        <v>124</v>
-      </c>
-      <c r="H41" t="s">
-        <v>125</v>
-      </c>
-      <c r="I41" s="12">
-        <v>45108</v>
-      </c>
-      <c r="J41" t="s">
-        <v>126</v>
-      </c>
-      <c r="K41" t="s">
-        <v>127</v>
-      </c>
-      <c r="L41" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B42">
-        <v>2030</v>
-      </c>
-      <c r="C42" t="s">
-        <v>120</v>
-      </c>
-      <c r="D42" t="s">
-        <v>118</v>
-      </c>
-      <c r="E42">
-        <v>64.099999999999994</v>
-      </c>
-      <c r="F42" t="s">
-        <v>123</v>
-      </c>
-      <c r="G42" t="s">
-        <v>124</v>
-      </c>
-      <c r="H42" t="s">
-        <v>125</v>
-      </c>
-      <c r="I42" s="12">
-        <v>45108</v>
-      </c>
-      <c r="J42" t="s">
-        <v>126</v>
-      </c>
-      <c r="K42" t="s">
-        <v>127</v>
-      </c>
-      <c r="L42" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B43">
-        <v>2030</v>
-      </c>
-      <c r="C43" t="s">
-        <v>122</v>
-      </c>
-      <c r="D43" t="s">
-        <v>121</v>
-      </c>
-      <c r="E43">
-        <v>72</v>
-      </c>
-      <c r="F43" t="s">
-        <v>123</v>
-      </c>
-      <c r="G43" t="s">
-        <v>124</v>
-      </c>
-      <c r="H43" t="s">
-        <v>125</v>
-      </c>
-      <c r="I43" s="12">
-        <v>45108</v>
-      </c>
-      <c r="J43" t="s">
-        <v>126</v>
-      </c>
-      <c r="K43" t="s">
-        <v>127</v>
-      </c>
-      <c r="L43" t="s">
-        <v>128</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2954,12 +2983,12 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s">
         <v>69</v>
@@ -2988,7 +3017,7 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -6597,7 +6626,7 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B250">
         <v>2000</v>
@@ -6723,7 +6752,7 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B259">
         <v>2001</v>
@@ -6849,7 +6878,7 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B268">
         <v>2002</v>
@@ -6975,7 +7004,7 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B277">
         <v>2003</v>
@@ -7101,7 +7130,7 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B286">
         <v>2004</v>
@@ -7227,7 +7256,7 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B295">
         <v>2005</v>
@@ -7353,7 +7382,7 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B304">
         <v>2006</v>
@@ -7479,7 +7508,7 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B313">
         <v>2007</v>
@@ -7605,7 +7634,7 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B322">
         <v>2008</v>
@@ -7731,7 +7760,7 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B331">
         <v>2009</v>
@@ -7857,7 +7886,7 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B340">
         <v>2010</v>
@@ -7983,7 +8012,7 @@
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B349">
         <v>2011</v>
@@ -8109,7 +8138,7 @@
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B358">
         <v>2012</v>
@@ -8235,7 +8264,7 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B367">
         <v>2013</v>
@@ -8361,7 +8390,7 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B376">
         <v>2014</v>
@@ -8487,7 +8516,7 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B385">
         <v>2015</v>
@@ -8613,7 +8642,7 @@
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B394">
         <v>2016</v>
@@ -8739,7 +8768,7 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B403">
         <v>2017</v>
@@ -8865,7 +8894,7 @@
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B412">
         <v>2018</v>
@@ -8991,7 +9020,7 @@
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B421">
         <v>2019</v>
@@ -9117,7 +9146,7 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B430">
         <v>2020</v>
@@ -9243,7 +9272,7 @@
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B439">
         <v>2021</v>
@@ -9369,7 +9398,7 @@
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B448">
         <v>2022</v>
@@ -9495,7 +9524,7 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B457">
         <v>2023</v>
@@ -10573,7 +10602,7 @@
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A534" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B534">
         <v>2018</v>
@@ -10587,7 +10616,7 @@
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A535" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B535">
         <v>2019</v>
@@ -10601,7 +10630,7 @@
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A536" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B536">
         <v>2020</v>
@@ -10615,7 +10644,7 @@
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A537" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B537">
         <v>2021</v>
@@ -10629,7 +10658,7 @@
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A538" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B538">
         <v>2022</v>
@@ -10643,7 +10672,7 @@
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A539" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B539">
         <v>2023</v>
@@ -10657,7 +10686,7 @@
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A540" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B540">
         <v>2024</v>
@@ -10671,7 +10700,7 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B541">
         <v>2011</v>
@@ -10685,7 +10714,7 @@
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A542" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B542">
         <v>2012</v>
@@ -10699,7 +10728,7 @@
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A543" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B543">
         <v>2013</v>
@@ -10713,7 +10742,7 @@
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A544" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B544">
         <v>2014</v>
@@ -10727,7 +10756,7 @@
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A545" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B545">
         <v>2015</v>
@@ -10741,7 +10770,7 @@
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A546" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B546">
         <v>2016</v>
@@ -10755,7 +10784,7 @@
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A547" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B547">
         <v>2017</v>
@@ -10769,7 +10798,7 @@
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A548" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B548">
         <v>2004</v>
@@ -10783,7 +10812,7 @@
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A549" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B549">
         <v>2005</v>
@@ -10797,7 +10826,7 @@
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B550">
         <v>2006</v>
@@ -10811,7 +10840,7 @@
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A551" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B551">
         <v>2007</v>
@@ -10825,7 +10854,7 @@
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A552" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B552">
         <v>2008</v>
@@ -10839,7 +10868,7 @@
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A553" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B553">
         <v>2009</v>
@@ -10853,7 +10882,7 @@
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A554" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B554">
         <v>2010</v>
@@ -10867,7 +10896,7 @@
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A555" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B555">
         <v>2000</v>
@@ -10881,7 +10910,7 @@
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A556" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B556">
         <v>2001</v>
@@ -10895,7 +10924,7 @@
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A557" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B557">
         <v>2002</v>
@@ -10909,7 +10938,7 @@
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A558" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B558">
         <v>2003</v>
@@ -10923,7 +10952,7 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B559">
         <v>2002</v>
@@ -10937,7 +10966,7 @@
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A560" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B560">
         <v>2003</v>
@@ -10951,7 +10980,7 @@
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A561" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B561">
         <v>2004</v>
@@ -10965,7 +10994,7 @@
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A562" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B562">
         <v>2005</v>
@@ -10979,7 +11008,7 @@
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A563" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B563">
         <v>2006</v>
@@ -10993,7 +11022,7 @@
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A564" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B564">
         <v>2007</v>
@@ -11007,7 +11036,7 @@
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A565" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B565">
         <v>2008</v>
@@ -11021,7 +11050,7 @@
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A566" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B566">
         <v>2009</v>
@@ -11035,7 +11064,7 @@
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A567" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B567">
         <v>2010</v>
@@ -11049,7 +11078,7 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B568">
         <v>2011</v>
@@ -11063,7 +11092,7 @@
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A569" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B569">
         <v>2012</v>
@@ -11077,7 +11106,7 @@
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A570" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B570">
         <v>2013</v>
@@ -11091,7 +11120,7 @@
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A571" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B571">
         <v>2014</v>
@@ -11105,7 +11134,7 @@
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A572" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B572">
         <v>2015</v>
@@ -11119,7 +11148,7 @@
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A573" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B573">
         <v>2016</v>
@@ -11133,7 +11162,7 @@
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A574" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B574">
         <v>2017</v>
@@ -11147,7 +11176,7 @@
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A575" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B575">
         <v>2018</v>
@@ -11161,7 +11190,7 @@
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A576" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B576">
         <v>2019</v>
@@ -11175,7 +11204,7 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B577">
         <v>2020</v>
@@ -11189,7 +11218,7 @@
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A578" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B578">
         <v>2021</v>
@@ -11203,7 +11232,7 @@
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A579" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B579">
         <v>2022</v>
@@ -11217,7 +11246,7 @@
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A580" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B580">
         <v>2000</v>
@@ -11231,7 +11260,7 @@
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A581" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B581">
         <v>2001</v>
@@ -11245,7 +11274,7 @@
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A582" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B582">
         <v>2023</v>
@@ -11259,7 +11288,7 @@
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A583" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B583">
         <v>2024</v>
@@ -13737,7 +13766,7 @@
     </row>
     <row r="760" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A760" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B760">
         <v>2018</v>
@@ -13751,7 +13780,7 @@
     </row>
     <row r="761" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A761" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B761">
         <v>2019</v>
@@ -13765,7 +13794,7 @@
     </row>
     <row r="762" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A762" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B762">
         <v>2020</v>
@@ -13779,7 +13808,7 @@
     </row>
     <row r="763" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A763" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B763">
         <v>2021</v>
@@ -13793,7 +13822,7 @@
     </row>
     <row r="764" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A764" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B764">
         <v>2022</v>
@@ -13807,7 +13836,7 @@
     </row>
     <row r="765" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A765" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B765">
         <v>2023</v>
@@ -13821,7 +13850,7 @@
     </row>
     <row r="766" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A766" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B766">
         <v>2024</v>
@@ -13835,7 +13864,7 @@
     </row>
     <row r="767" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A767" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B767">
         <v>2011</v>
@@ -13849,7 +13878,7 @@
     </row>
     <row r="768" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A768" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B768">
         <v>2012</v>
@@ -13863,7 +13892,7 @@
     </row>
     <row r="769" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A769" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B769">
         <v>2013</v>
@@ -13877,7 +13906,7 @@
     </row>
     <row r="770" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A770" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B770">
         <v>2014</v>
@@ -13891,7 +13920,7 @@
     </row>
     <row r="771" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A771" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B771">
         <v>2015</v>
@@ -13905,7 +13934,7 @@
     </row>
     <row r="772" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A772" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B772">
         <v>2016</v>
@@ -13919,7 +13948,7 @@
     </row>
     <row r="773" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A773" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B773">
         <v>2017</v>
@@ -13933,7 +13962,7 @@
     </row>
     <row r="774" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A774" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B774">
         <v>2004</v>
@@ -13947,7 +13976,7 @@
     </row>
     <row r="775" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A775" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B775">
         <v>2005</v>
@@ -13961,7 +13990,7 @@
     </row>
     <row r="776" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A776" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B776">
         <v>2006</v>
@@ -13975,7 +14004,7 @@
     </row>
     <row r="777" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A777" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B777">
         <v>2007</v>
@@ -13989,7 +14018,7 @@
     </row>
     <row r="778" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A778" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B778">
         <v>2008</v>
@@ -14003,7 +14032,7 @@
     </row>
     <row r="779" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A779" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B779">
         <v>2009</v>
@@ -14017,7 +14046,7 @@
     </row>
     <row r="780" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A780" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B780">
         <v>2010</v>
@@ -14031,7 +14060,7 @@
     </row>
     <row r="781" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A781" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B781">
         <v>2000</v>
@@ -14045,7 +14074,7 @@
     </row>
     <row r="782" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A782" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B782">
         <v>2001</v>
@@ -14059,7 +14088,7 @@
     </row>
     <row r="783" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A783" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B783">
         <v>2002</v>
@@ -14073,7 +14102,7 @@
     </row>
     <row r="784" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A784" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B784">
         <v>2003</v>
@@ -14087,7 +14116,7 @@
     </row>
     <row r="785" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A785" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B785">
         <v>2002</v>
@@ -14101,7 +14130,7 @@
     </row>
     <row r="786" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A786" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B786">
         <v>2003</v>
@@ -14115,7 +14144,7 @@
     </row>
     <row r="787" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A787" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B787">
         <v>2004</v>
@@ -14129,7 +14158,7 @@
     </row>
     <row r="788" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A788" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B788">
         <v>2005</v>
@@ -14143,7 +14172,7 @@
     </row>
     <row r="789" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A789" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B789">
         <v>2006</v>
@@ -14157,7 +14186,7 @@
     </row>
     <row r="790" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A790" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B790">
         <v>2007</v>
@@ -14171,7 +14200,7 @@
     </row>
     <row r="791" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A791" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B791">
         <v>2008</v>
@@ -14185,7 +14214,7 @@
     </row>
     <row r="792" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A792" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B792">
         <v>2009</v>
@@ -14199,7 +14228,7 @@
     </row>
     <row r="793" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A793" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B793">
         <v>2010</v>
@@ -14213,7 +14242,7 @@
     </row>
     <row r="794" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A794" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B794">
         <v>2011</v>
@@ -14227,7 +14256,7 @@
     </row>
     <row r="795" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A795" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B795">
         <v>2012</v>
@@ -14241,7 +14270,7 @@
     </row>
     <row r="796" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A796" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B796">
         <v>2013</v>
@@ -14255,7 +14284,7 @@
     </row>
     <row r="797" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A797" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B797">
         <v>2014</v>
@@ -14269,7 +14298,7 @@
     </row>
     <row r="798" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A798" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B798">
         <v>2015</v>
@@ -14283,7 +14312,7 @@
     </row>
     <row r="799" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A799" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B799">
         <v>2016</v>
@@ -14297,7 +14326,7 @@
     </row>
     <row r="800" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A800" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B800">
         <v>2017</v>
@@ -14311,7 +14340,7 @@
     </row>
     <row r="801" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A801" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B801">
         <v>2018</v>
@@ -14325,7 +14354,7 @@
     </row>
     <row r="802" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A802" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B802">
         <v>2019</v>
@@ -14339,7 +14368,7 @@
     </row>
     <row r="803" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A803" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B803">
         <v>2020</v>
@@ -14353,7 +14382,7 @@
     </row>
     <row r="804" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A804" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B804">
         <v>2021</v>
@@ -14367,7 +14396,7 @@
     </row>
     <row r="805" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A805" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B805">
         <v>2022</v>
@@ -14381,7 +14410,7 @@
     </row>
     <row r="806" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A806" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B806">
         <v>2000</v>
@@ -14395,7 +14424,7 @@
     </row>
     <row r="807" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A807" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B807">
         <v>2001</v>
